--- a/MySchoolChecks/absences_template.xlsx
+++ b/MySchoolChecks/absences_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Απουσίες" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Οδηγίες" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Απουσίες" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Οδηγίες" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="d/m/yyyy"/>
+  </numFmts>
   <fonts count="6">
     <font>
       <name val="Calibri"/>
@@ -84,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -97,6 +99,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -505,15 +508,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:G500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -529,24 +533,2025 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Από</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Έως</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Α.Φ.Μ.</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Επώνυμο</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Όνομα</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="C2" s="6" t="n"/>
+      <c r="D2" s="6" t="n"/>
+    </row>
+    <row r="3">
+      <c r="C3" s="6" t="n"/>
+      <c r="D3" s="6" t="n"/>
+    </row>
+    <row r="4">
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+    </row>
+    <row r="20">
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="6" t="n"/>
+    </row>
+    <row r="25">
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+    </row>
+    <row r="27">
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+    </row>
+    <row r="29">
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30">
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31">
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33">
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34">
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+    </row>
+    <row r="35">
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36">
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+    </row>
+    <row r="37">
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+    </row>
+    <row r="38">
+      <c r="C38" s="6" t="n"/>
+      <c r="D38" s="6" t="n"/>
+    </row>
+    <row r="39">
+      <c r="C39" s="6" t="n"/>
+      <c r="D39" s="6" t="n"/>
+    </row>
+    <row r="40">
+      <c r="C40" s="6" t="n"/>
+      <c r="D40" s="6" t="n"/>
+    </row>
+    <row r="41">
+      <c r="C41" s="6" t="n"/>
+      <c r="D41" s="6" t="n"/>
+    </row>
+    <row r="42">
+      <c r="C42" s="6" t="n"/>
+      <c r="D42" s="6" t="n"/>
+    </row>
+    <row r="43">
+      <c r="C43" s="6" t="n"/>
+      <c r="D43" s="6" t="n"/>
+    </row>
+    <row r="44">
+      <c r="C44" s="6" t="n"/>
+      <c r="D44" s="6" t="n"/>
+    </row>
+    <row r="45">
+      <c r="C45" s="6" t="n"/>
+      <c r="D45" s="6" t="n"/>
+    </row>
+    <row r="46">
+      <c r="C46" s="6" t="n"/>
+      <c r="D46" s="6" t="n"/>
+    </row>
+    <row r="47">
+      <c r="C47" s="6" t="n"/>
+      <c r="D47" s="6" t="n"/>
+    </row>
+    <row r="48">
+      <c r="C48" s="6" t="n"/>
+      <c r="D48" s="6" t="n"/>
+    </row>
+    <row r="49">
+      <c r="C49" s="6" t="n"/>
+      <c r="D49" s="6" t="n"/>
+    </row>
+    <row r="50">
+      <c r="C50" s="6" t="n"/>
+      <c r="D50" s="6" t="n"/>
+    </row>
+    <row r="51">
+      <c r="C51" s="6" t="n"/>
+      <c r="D51" s="6" t="n"/>
+    </row>
+    <row r="52">
+      <c r="C52" s="6" t="n"/>
+      <c r="D52" s="6" t="n"/>
+    </row>
+    <row r="53">
+      <c r="C53" s="6" t="n"/>
+      <c r="D53" s="6" t="n"/>
+    </row>
+    <row r="54">
+      <c r="C54" s="6" t="n"/>
+      <c r="D54" s="6" t="n"/>
+    </row>
+    <row r="55">
+      <c r="C55" s="6" t="n"/>
+      <c r="D55" s="6" t="n"/>
+    </row>
+    <row r="56">
+      <c r="C56" s="6" t="n"/>
+      <c r="D56" s="6" t="n"/>
+    </row>
+    <row r="57">
+      <c r="C57" s="6" t="n"/>
+      <c r="D57" s="6" t="n"/>
+    </row>
+    <row r="58">
+      <c r="C58" s="6" t="n"/>
+      <c r="D58" s="6" t="n"/>
+    </row>
+    <row r="59">
+      <c r="C59" s="6" t="n"/>
+      <c r="D59" s="6" t="n"/>
+    </row>
+    <row r="60">
+      <c r="C60" s="6" t="n"/>
+      <c r="D60" s="6" t="n"/>
+    </row>
+    <row r="61">
+      <c r="C61" s="6" t="n"/>
+      <c r="D61" s="6" t="n"/>
+    </row>
+    <row r="62">
+      <c r="C62" s="6" t="n"/>
+      <c r="D62" s="6" t="n"/>
+    </row>
+    <row r="63">
+      <c r="C63" s="6" t="n"/>
+      <c r="D63" s="6" t="n"/>
+    </row>
+    <row r="64">
+      <c r="C64" s="6" t="n"/>
+      <c r="D64" s="6" t="n"/>
+    </row>
+    <row r="65">
+      <c r="C65" s="6" t="n"/>
+      <c r="D65" s="6" t="n"/>
+    </row>
+    <row r="66">
+      <c r="C66" s="6" t="n"/>
+      <c r="D66" s="6" t="n"/>
+    </row>
+    <row r="67">
+      <c r="C67" s="6" t="n"/>
+      <c r="D67" s="6" t="n"/>
+    </row>
+    <row r="68">
+      <c r="C68" s="6" t="n"/>
+      <c r="D68" s="6" t="n"/>
+    </row>
+    <row r="69">
+      <c r="C69" s="6" t="n"/>
+      <c r="D69" s="6" t="n"/>
+    </row>
+    <row r="70">
+      <c r="C70" s="6" t="n"/>
+      <c r="D70" s="6" t="n"/>
+    </row>
+    <row r="71">
+      <c r="C71" s="6" t="n"/>
+      <c r="D71" s="6" t="n"/>
+    </row>
+    <row r="72">
+      <c r="C72" s="6" t="n"/>
+      <c r="D72" s="6" t="n"/>
+    </row>
+    <row r="73">
+      <c r="C73" s="6" t="n"/>
+      <c r="D73" s="6" t="n"/>
+    </row>
+    <row r="74">
+      <c r="C74" s="6" t="n"/>
+      <c r="D74" s="6" t="n"/>
+    </row>
+    <row r="75">
+      <c r="C75" s="6" t="n"/>
+      <c r="D75" s="6" t="n"/>
+    </row>
+    <row r="76">
+      <c r="C76" s="6" t="n"/>
+      <c r="D76" s="6" t="n"/>
+    </row>
+    <row r="77">
+      <c r="C77" s="6" t="n"/>
+      <c r="D77" s="6" t="n"/>
+    </row>
+    <row r="78">
+      <c r="C78" s="6" t="n"/>
+      <c r="D78" s="6" t="n"/>
+    </row>
+    <row r="79">
+      <c r="C79" s="6" t="n"/>
+      <c r="D79" s="6" t="n"/>
+    </row>
+    <row r="80">
+      <c r="C80" s="6" t="n"/>
+      <c r="D80" s="6" t="n"/>
+    </row>
+    <row r="81">
+      <c r="C81" s="6" t="n"/>
+      <c r="D81" s="6" t="n"/>
+    </row>
+    <row r="82">
+      <c r="C82" s="6" t="n"/>
+      <c r="D82" s="6" t="n"/>
+    </row>
+    <row r="83">
+      <c r="C83" s="6" t="n"/>
+      <c r="D83" s="6" t="n"/>
+    </row>
+    <row r="84">
+      <c r="C84" s="6" t="n"/>
+      <c r="D84" s="6" t="n"/>
+    </row>
+    <row r="85">
+      <c r="C85" s="6" t="n"/>
+      <c r="D85" s="6" t="n"/>
+    </row>
+    <row r="86">
+      <c r="C86" s="6" t="n"/>
+      <c r="D86" s="6" t="n"/>
+    </row>
+    <row r="87">
+      <c r="C87" s="6" t="n"/>
+      <c r="D87" s="6" t="n"/>
+    </row>
+    <row r="88">
+      <c r="C88" s="6" t="n"/>
+      <c r="D88" s="6" t="n"/>
+    </row>
+    <row r="89">
+      <c r="C89" s="6" t="n"/>
+      <c r="D89" s="6" t="n"/>
+    </row>
+    <row r="90">
+      <c r="C90" s="6" t="n"/>
+      <c r="D90" s="6" t="n"/>
+    </row>
+    <row r="91">
+      <c r="C91" s="6" t="n"/>
+      <c r="D91" s="6" t="n"/>
+    </row>
+    <row r="92">
+      <c r="C92" s="6" t="n"/>
+      <c r="D92" s="6" t="n"/>
+    </row>
+    <row r="93">
+      <c r="C93" s="6" t="n"/>
+      <c r="D93" s="6" t="n"/>
+    </row>
+    <row r="94">
+      <c r="C94" s="6" t="n"/>
+      <c r="D94" s="6" t="n"/>
+    </row>
+    <row r="95">
+      <c r="C95" s="6" t="n"/>
+      <c r="D95" s="6" t="n"/>
+    </row>
+    <row r="96">
+      <c r="C96" s="6" t="n"/>
+      <c r="D96" s="6" t="n"/>
+    </row>
+    <row r="97">
+      <c r="C97" s="6" t="n"/>
+      <c r="D97" s="6" t="n"/>
+    </row>
+    <row r="98">
+      <c r="C98" s="6" t="n"/>
+      <c r="D98" s="6" t="n"/>
+    </row>
+    <row r="99">
+      <c r="C99" s="6" t="n"/>
+      <c r="D99" s="6" t="n"/>
+    </row>
+    <row r="100">
+      <c r="C100" s="6" t="n"/>
+      <c r="D100" s="6" t="n"/>
+    </row>
+    <row r="101">
+      <c r="C101" s="6" t="n"/>
+      <c r="D101" s="6" t="n"/>
+    </row>
+    <row r="102">
+      <c r="C102" s="6" t="n"/>
+      <c r="D102" s="6" t="n"/>
+    </row>
+    <row r="103">
+      <c r="C103" s="6" t="n"/>
+      <c r="D103" s="6" t="n"/>
+    </row>
+    <row r="104">
+      <c r="C104" s="6" t="n"/>
+      <c r="D104" s="6" t="n"/>
+    </row>
+    <row r="105">
+      <c r="C105" s="6" t="n"/>
+      <c r="D105" s="6" t="n"/>
+    </row>
+    <row r="106">
+      <c r="C106" s="6" t="n"/>
+      <c r="D106" s="6" t="n"/>
+    </row>
+    <row r="107">
+      <c r="C107" s="6" t="n"/>
+      <c r="D107" s="6" t="n"/>
+    </row>
+    <row r="108">
+      <c r="C108" s="6" t="n"/>
+      <c r="D108" s="6" t="n"/>
+    </row>
+    <row r="109">
+      <c r="C109" s="6" t="n"/>
+      <c r="D109" s="6" t="n"/>
+    </row>
+    <row r="110">
+      <c r="C110" s="6" t="n"/>
+      <c r="D110" s="6" t="n"/>
+    </row>
+    <row r="111">
+      <c r="C111" s="6" t="n"/>
+      <c r="D111" s="6" t="n"/>
+    </row>
+    <row r="112">
+      <c r="C112" s="6" t="n"/>
+      <c r="D112" s="6" t="n"/>
+    </row>
+    <row r="113">
+      <c r="C113" s="6" t="n"/>
+      <c r="D113" s="6" t="n"/>
+    </row>
+    <row r="114">
+      <c r="C114" s="6" t="n"/>
+      <c r="D114" s="6" t="n"/>
+    </row>
+    <row r="115">
+      <c r="C115" s="6" t="n"/>
+      <c r="D115" s="6" t="n"/>
+    </row>
+    <row r="116">
+      <c r="C116" s="6" t="n"/>
+      <c r="D116" s="6" t="n"/>
+    </row>
+    <row r="117">
+      <c r="C117" s="6" t="n"/>
+      <c r="D117" s="6" t="n"/>
+    </row>
+    <row r="118">
+      <c r="C118" s="6" t="n"/>
+      <c r="D118" s="6" t="n"/>
+    </row>
+    <row r="119">
+      <c r="C119" s="6" t="n"/>
+      <c r="D119" s="6" t="n"/>
+    </row>
+    <row r="120">
+      <c r="C120" s="6" t="n"/>
+      <c r="D120" s="6" t="n"/>
+    </row>
+    <row r="121">
+      <c r="C121" s="6" t="n"/>
+      <c r="D121" s="6" t="n"/>
+    </row>
+    <row r="122">
+      <c r="C122" s="6" t="n"/>
+      <c r="D122" s="6" t="n"/>
+    </row>
+    <row r="123">
+      <c r="C123" s="6" t="n"/>
+      <c r="D123" s="6" t="n"/>
+    </row>
+    <row r="124">
+      <c r="C124" s="6" t="n"/>
+      <c r="D124" s="6" t="n"/>
+    </row>
+    <row r="125">
+      <c r="C125" s="6" t="n"/>
+      <c r="D125" s="6" t="n"/>
+    </row>
+    <row r="126">
+      <c r="C126" s="6" t="n"/>
+      <c r="D126" s="6" t="n"/>
+    </row>
+    <row r="127">
+      <c r="C127" s="6" t="n"/>
+      <c r="D127" s="6" t="n"/>
+    </row>
+    <row r="128">
+      <c r="C128" s="6" t="n"/>
+      <c r="D128" s="6" t="n"/>
+    </row>
+    <row r="129">
+      <c r="C129" s="6" t="n"/>
+      <c r="D129" s="6" t="n"/>
+    </row>
+    <row r="130">
+      <c r="C130" s="6" t="n"/>
+      <c r="D130" s="6" t="n"/>
+    </row>
+    <row r="131">
+      <c r="C131" s="6" t="n"/>
+      <c r="D131" s="6" t="n"/>
+    </row>
+    <row r="132">
+      <c r="C132" s="6" t="n"/>
+      <c r="D132" s="6" t="n"/>
+    </row>
+    <row r="133">
+      <c r="C133" s="6" t="n"/>
+      <c r="D133" s="6" t="n"/>
+    </row>
+    <row r="134">
+      <c r="C134" s="6" t="n"/>
+      <c r="D134" s="6" t="n"/>
+    </row>
+    <row r="135">
+      <c r="C135" s="6" t="n"/>
+      <c r="D135" s="6" t="n"/>
+    </row>
+    <row r="136">
+      <c r="C136" s="6" t="n"/>
+      <c r="D136" s="6" t="n"/>
+    </row>
+    <row r="137">
+      <c r="C137" s="6" t="n"/>
+      <c r="D137" s="6" t="n"/>
+    </row>
+    <row r="138">
+      <c r="C138" s="6" t="n"/>
+      <c r="D138" s="6" t="n"/>
+    </row>
+    <row r="139">
+      <c r="C139" s="6" t="n"/>
+      <c r="D139" s="6" t="n"/>
+    </row>
+    <row r="140">
+      <c r="C140" s="6" t="n"/>
+      <c r="D140" s="6" t="n"/>
+    </row>
+    <row r="141">
+      <c r="C141" s="6" t="n"/>
+      <c r="D141" s="6" t="n"/>
+    </row>
+    <row r="142">
+      <c r="C142" s="6" t="n"/>
+      <c r="D142" s="6" t="n"/>
+    </row>
+    <row r="143">
+      <c r="C143" s="6" t="n"/>
+      <c r="D143" s="6" t="n"/>
+    </row>
+    <row r="144">
+      <c r="C144" s="6" t="n"/>
+      <c r="D144" s="6" t="n"/>
+    </row>
+    <row r="145">
+      <c r="C145" s="6" t="n"/>
+      <c r="D145" s="6" t="n"/>
+    </row>
+    <row r="146">
+      <c r="C146" s="6" t="n"/>
+      <c r="D146" s="6" t="n"/>
+    </row>
+    <row r="147">
+      <c r="C147" s="6" t="n"/>
+      <c r="D147" s="6" t="n"/>
+    </row>
+    <row r="148">
+      <c r="C148" s="6" t="n"/>
+      <c r="D148" s="6" t="n"/>
+    </row>
+    <row r="149">
+      <c r="C149" s="6" t="n"/>
+      <c r="D149" s="6" t="n"/>
+    </row>
+    <row r="150">
+      <c r="C150" s="6" t="n"/>
+      <c r="D150" s="6" t="n"/>
+    </row>
+    <row r="151">
+      <c r="C151" s="6" t="n"/>
+      <c r="D151" s="6" t="n"/>
+    </row>
+    <row r="152">
+      <c r="C152" s="6" t="n"/>
+      <c r="D152" s="6" t="n"/>
+    </row>
+    <row r="153">
+      <c r="C153" s="6" t="n"/>
+      <c r="D153" s="6" t="n"/>
+    </row>
+    <row r="154">
+      <c r="C154" s="6" t="n"/>
+      <c r="D154" s="6" t="n"/>
+    </row>
+    <row r="155">
+      <c r="C155" s="6" t="n"/>
+      <c r="D155" s="6" t="n"/>
+    </row>
+    <row r="156">
+      <c r="C156" s="6" t="n"/>
+      <c r="D156" s="6" t="n"/>
+    </row>
+    <row r="157">
+      <c r="C157" s="6" t="n"/>
+      <c r="D157" s="6" t="n"/>
+    </row>
+    <row r="158">
+      <c r="C158" s="6" t="n"/>
+      <c r="D158" s="6" t="n"/>
+    </row>
+    <row r="159">
+      <c r="C159" s="6" t="n"/>
+      <c r="D159" s="6" t="n"/>
+    </row>
+    <row r="160">
+      <c r="C160" s="6" t="n"/>
+      <c r="D160" s="6" t="n"/>
+    </row>
+    <row r="161">
+      <c r="C161" s="6" t="n"/>
+      <c r="D161" s="6" t="n"/>
+    </row>
+    <row r="162">
+      <c r="C162" s="6" t="n"/>
+      <c r="D162" s="6" t="n"/>
+    </row>
+    <row r="163">
+      <c r="C163" s="6" t="n"/>
+      <c r="D163" s="6" t="n"/>
+    </row>
+    <row r="164">
+      <c r="C164" s="6" t="n"/>
+      <c r="D164" s="6" t="n"/>
+    </row>
+    <row r="165">
+      <c r="C165" s="6" t="n"/>
+      <c r="D165" s="6" t="n"/>
+    </row>
+    <row r="166">
+      <c r="C166" s="6" t="n"/>
+      <c r="D166" s="6" t="n"/>
+    </row>
+    <row r="167">
+      <c r="C167" s="6" t="n"/>
+      <c r="D167" s="6" t="n"/>
+    </row>
+    <row r="168">
+      <c r="C168" s="6" t="n"/>
+      <c r="D168" s="6" t="n"/>
+    </row>
+    <row r="169">
+      <c r="C169" s="6" t="n"/>
+      <c r="D169" s="6" t="n"/>
+    </row>
+    <row r="170">
+      <c r="C170" s="6" t="n"/>
+      <c r="D170" s="6" t="n"/>
+    </row>
+    <row r="171">
+      <c r="C171" s="6" t="n"/>
+      <c r="D171" s="6" t="n"/>
+    </row>
+    <row r="172">
+      <c r="C172" s="6" t="n"/>
+      <c r="D172" s="6" t="n"/>
+    </row>
+    <row r="173">
+      <c r="C173" s="6" t="n"/>
+      <c r="D173" s="6" t="n"/>
+    </row>
+    <row r="174">
+      <c r="C174" s="6" t="n"/>
+      <c r="D174" s="6" t="n"/>
+    </row>
+    <row r="175">
+      <c r="C175" s="6" t="n"/>
+      <c r="D175" s="6" t="n"/>
+    </row>
+    <row r="176">
+      <c r="C176" s="6" t="n"/>
+      <c r="D176" s="6" t="n"/>
+    </row>
+    <row r="177">
+      <c r="C177" s="6" t="n"/>
+      <c r="D177" s="6" t="n"/>
+    </row>
+    <row r="178">
+      <c r="C178" s="6" t="n"/>
+      <c r="D178" s="6" t="n"/>
+    </row>
+    <row r="179">
+      <c r="C179" s="6" t="n"/>
+      <c r="D179" s="6" t="n"/>
+    </row>
+    <row r="180">
+      <c r="C180" s="6" t="n"/>
+      <c r="D180" s="6" t="n"/>
+    </row>
+    <row r="181">
+      <c r="C181" s="6" t="n"/>
+      <c r="D181" s="6" t="n"/>
+    </row>
+    <row r="182">
+      <c r="C182" s="6" t="n"/>
+      <c r="D182" s="6" t="n"/>
+    </row>
+    <row r="183">
+      <c r="C183" s="6" t="n"/>
+      <c r="D183" s="6" t="n"/>
+    </row>
+    <row r="184">
+      <c r="C184" s="6" t="n"/>
+      <c r="D184" s="6" t="n"/>
+    </row>
+    <row r="185">
+      <c r="C185" s="6" t="n"/>
+      <c r="D185" s="6" t="n"/>
+    </row>
+    <row r="186">
+      <c r="C186" s="6" t="n"/>
+      <c r="D186" s="6" t="n"/>
+    </row>
+    <row r="187">
+      <c r="C187" s="6" t="n"/>
+      <c r="D187" s="6" t="n"/>
+    </row>
+    <row r="188">
+      <c r="C188" s="6" t="n"/>
+      <c r="D188" s="6" t="n"/>
+    </row>
+    <row r="189">
+      <c r="C189" s="6" t="n"/>
+      <c r="D189" s="6" t="n"/>
+    </row>
+    <row r="190">
+      <c r="C190" s="6" t="n"/>
+      <c r="D190" s="6" t="n"/>
+    </row>
+    <row r="191">
+      <c r="C191" s="6" t="n"/>
+      <c r="D191" s="6" t="n"/>
+    </row>
+    <row r="192">
+      <c r="C192" s="6" t="n"/>
+      <c r="D192" s="6" t="n"/>
+    </row>
+    <row r="193">
+      <c r="C193" s="6" t="n"/>
+      <c r="D193" s="6" t="n"/>
+    </row>
+    <row r="194">
+      <c r="C194" s="6" t="n"/>
+      <c r="D194" s="6" t="n"/>
+    </row>
+    <row r="195">
+      <c r="C195" s="6" t="n"/>
+      <c r="D195" s="6" t="n"/>
+    </row>
+    <row r="196">
+      <c r="C196" s="6" t="n"/>
+      <c r="D196" s="6" t="n"/>
+    </row>
+    <row r="197">
+      <c r="C197" s="6" t="n"/>
+      <c r="D197" s="6" t="n"/>
+    </row>
+    <row r="198">
+      <c r="C198" s="6" t="n"/>
+      <c r="D198" s="6" t="n"/>
+    </row>
+    <row r="199">
+      <c r="C199" s="6" t="n"/>
+      <c r="D199" s="6" t="n"/>
+    </row>
+    <row r="200">
+      <c r="C200" s="6" t="n"/>
+      <c r="D200" s="6" t="n"/>
+    </row>
+    <row r="201">
+      <c r="C201" s="6" t="n"/>
+      <c r="D201" s="6" t="n"/>
+    </row>
+    <row r="202">
+      <c r="C202" s="6" t="n"/>
+      <c r="D202" s="6" t="n"/>
+    </row>
+    <row r="203">
+      <c r="C203" s="6" t="n"/>
+      <c r="D203" s="6" t="n"/>
+    </row>
+    <row r="204">
+      <c r="C204" s="6" t="n"/>
+      <c r="D204" s="6" t="n"/>
+    </row>
+    <row r="205">
+      <c r="C205" s="6" t="n"/>
+      <c r="D205" s="6" t="n"/>
+    </row>
+    <row r="206">
+      <c r="C206" s="6" t="n"/>
+      <c r="D206" s="6" t="n"/>
+    </row>
+    <row r="207">
+      <c r="C207" s="6" t="n"/>
+      <c r="D207" s="6" t="n"/>
+    </row>
+    <row r="208">
+      <c r="C208" s="6" t="n"/>
+      <c r="D208" s="6" t="n"/>
+    </row>
+    <row r="209">
+      <c r="C209" s="6" t="n"/>
+      <c r="D209" s="6" t="n"/>
+    </row>
+    <row r="210">
+      <c r="C210" s="6" t="n"/>
+      <c r="D210" s="6" t="n"/>
+    </row>
+    <row r="211">
+      <c r="C211" s="6" t="n"/>
+      <c r="D211" s="6" t="n"/>
+    </row>
+    <row r="212">
+      <c r="C212" s="6" t="n"/>
+      <c r="D212" s="6" t="n"/>
+    </row>
+    <row r="213">
+      <c r="C213" s="6" t="n"/>
+      <c r="D213" s="6" t="n"/>
+    </row>
+    <row r="214">
+      <c r="C214" s="6" t="n"/>
+      <c r="D214" s="6" t="n"/>
+    </row>
+    <row r="215">
+      <c r="C215" s="6" t="n"/>
+      <c r="D215" s="6" t="n"/>
+    </row>
+    <row r="216">
+      <c r="C216" s="6" t="n"/>
+      <c r="D216" s="6" t="n"/>
+    </row>
+    <row r="217">
+      <c r="C217" s="6" t="n"/>
+      <c r="D217" s="6" t="n"/>
+    </row>
+    <row r="218">
+      <c r="C218" s="6" t="n"/>
+      <c r="D218" s="6" t="n"/>
+    </row>
+    <row r="219">
+      <c r="C219" s="6" t="n"/>
+      <c r="D219" s="6" t="n"/>
+    </row>
+    <row r="220">
+      <c r="C220" s="6" t="n"/>
+      <c r="D220" s="6" t="n"/>
+    </row>
+    <row r="221">
+      <c r="C221" s="6" t="n"/>
+      <c r="D221" s="6" t="n"/>
+    </row>
+    <row r="222">
+      <c r="C222" s="6" t="n"/>
+      <c r="D222" s="6" t="n"/>
+    </row>
+    <row r="223">
+      <c r="C223" s="6" t="n"/>
+      <c r="D223" s="6" t="n"/>
+    </row>
+    <row r="224">
+      <c r="C224" s="6" t="n"/>
+      <c r="D224" s="6" t="n"/>
+    </row>
+    <row r="225">
+      <c r="C225" s="6" t="n"/>
+      <c r="D225" s="6" t="n"/>
+    </row>
+    <row r="226">
+      <c r="C226" s="6" t="n"/>
+      <c r="D226" s="6" t="n"/>
+    </row>
+    <row r="227">
+      <c r="C227" s="6" t="n"/>
+      <c r="D227" s="6" t="n"/>
+    </row>
+    <row r="228">
+      <c r="C228" s="6" t="n"/>
+      <c r="D228" s="6" t="n"/>
+    </row>
+    <row r="229">
+      <c r="C229" s="6" t="n"/>
+      <c r="D229" s="6" t="n"/>
+    </row>
+    <row r="230">
+      <c r="C230" s="6" t="n"/>
+      <c r="D230" s="6" t="n"/>
+    </row>
+    <row r="231">
+      <c r="C231" s="6" t="n"/>
+      <c r="D231" s="6" t="n"/>
+    </row>
+    <row r="232">
+      <c r="C232" s="6" t="n"/>
+      <c r="D232" s="6" t="n"/>
+    </row>
+    <row r="233">
+      <c r="C233" s="6" t="n"/>
+      <c r="D233" s="6" t="n"/>
+    </row>
+    <row r="234">
+      <c r="C234" s="6" t="n"/>
+      <c r="D234" s="6" t="n"/>
+    </row>
+    <row r="235">
+      <c r="C235" s="6" t="n"/>
+      <c r="D235" s="6" t="n"/>
+    </row>
+    <row r="236">
+      <c r="C236" s="6" t="n"/>
+      <c r="D236" s="6" t="n"/>
+    </row>
+    <row r="237">
+      <c r="C237" s="6" t="n"/>
+      <c r="D237" s="6" t="n"/>
+    </row>
+    <row r="238">
+      <c r="C238" s="6" t="n"/>
+      <c r="D238" s="6" t="n"/>
+    </row>
+    <row r="239">
+      <c r="C239" s="6" t="n"/>
+      <c r="D239" s="6" t="n"/>
+    </row>
+    <row r="240">
+      <c r="C240" s="6" t="n"/>
+      <c r="D240" s="6" t="n"/>
+    </row>
+    <row r="241">
+      <c r="C241" s="6" t="n"/>
+      <c r="D241" s="6" t="n"/>
+    </row>
+    <row r="242">
+      <c r="C242" s="6" t="n"/>
+      <c r="D242" s="6" t="n"/>
+    </row>
+    <row r="243">
+      <c r="C243" s="6" t="n"/>
+      <c r="D243" s="6" t="n"/>
+    </row>
+    <row r="244">
+      <c r="C244" s="6" t="n"/>
+      <c r="D244" s="6" t="n"/>
+    </row>
+    <row r="245">
+      <c r="C245" s="6" t="n"/>
+      <c r="D245" s="6" t="n"/>
+    </row>
+    <row r="246">
+      <c r="C246" s="6" t="n"/>
+      <c r="D246" s="6" t="n"/>
+    </row>
+    <row r="247">
+      <c r="C247" s="6" t="n"/>
+      <c r="D247" s="6" t="n"/>
+    </row>
+    <row r="248">
+      <c r="C248" s="6" t="n"/>
+      <c r="D248" s="6" t="n"/>
+    </row>
+    <row r="249">
+      <c r="C249" s="6" t="n"/>
+      <c r="D249" s="6" t="n"/>
+    </row>
+    <row r="250">
+      <c r="C250" s="6" t="n"/>
+      <c r="D250" s="6" t="n"/>
+    </row>
+    <row r="251">
+      <c r="C251" s="6" t="n"/>
+      <c r="D251" s="6" t="n"/>
+    </row>
+    <row r="252">
+      <c r="C252" s="6" t="n"/>
+      <c r="D252" s="6" t="n"/>
+    </row>
+    <row r="253">
+      <c r="C253" s="6" t="n"/>
+      <c r="D253" s="6" t="n"/>
+    </row>
+    <row r="254">
+      <c r="C254" s="6" t="n"/>
+      <c r="D254" s="6" t="n"/>
+    </row>
+    <row r="255">
+      <c r="C255" s="6" t="n"/>
+      <c r="D255" s="6" t="n"/>
+    </row>
+    <row r="256">
+      <c r="C256" s="6" t="n"/>
+      <c r="D256" s="6" t="n"/>
+    </row>
+    <row r="257">
+      <c r="C257" s="6" t="n"/>
+      <c r="D257" s="6" t="n"/>
+    </row>
+    <row r="258">
+      <c r="C258" s="6" t="n"/>
+      <c r="D258" s="6" t="n"/>
+    </row>
+    <row r="259">
+      <c r="C259" s="6" t="n"/>
+      <c r="D259" s="6" t="n"/>
+    </row>
+    <row r="260">
+      <c r="C260" s="6" t="n"/>
+      <c r="D260" s="6" t="n"/>
+    </row>
+    <row r="261">
+      <c r="C261" s="6" t="n"/>
+      <c r="D261" s="6" t="n"/>
+    </row>
+    <row r="262">
+      <c r="C262" s="6" t="n"/>
+      <c r="D262" s="6" t="n"/>
+    </row>
+    <row r="263">
+      <c r="C263" s="6" t="n"/>
+      <c r="D263" s="6" t="n"/>
+    </row>
+    <row r="264">
+      <c r="C264" s="6" t="n"/>
+      <c r="D264" s="6" t="n"/>
+    </row>
+    <row r="265">
+      <c r="C265" s="6" t="n"/>
+      <c r="D265" s="6" t="n"/>
+    </row>
+    <row r="266">
+      <c r="C266" s="6" t="n"/>
+      <c r="D266" s="6" t="n"/>
+    </row>
+    <row r="267">
+      <c r="C267" s="6" t="n"/>
+      <c r="D267" s="6" t="n"/>
+    </row>
+    <row r="268">
+      <c r="C268" s="6" t="n"/>
+      <c r="D268" s="6" t="n"/>
+    </row>
+    <row r="269">
+      <c r="C269" s="6" t="n"/>
+      <c r="D269" s="6" t="n"/>
+    </row>
+    <row r="270">
+      <c r="C270" s="6" t="n"/>
+      <c r="D270" s="6" t="n"/>
+    </row>
+    <row r="271">
+      <c r="C271" s="6" t="n"/>
+      <c r="D271" s="6" t="n"/>
+    </row>
+    <row r="272">
+      <c r="C272" s="6" t="n"/>
+      <c r="D272" s="6" t="n"/>
+    </row>
+    <row r="273">
+      <c r="C273" s="6" t="n"/>
+      <c r="D273" s="6" t="n"/>
+    </row>
+    <row r="274">
+      <c r="C274" s="6" t="n"/>
+      <c r="D274" s="6" t="n"/>
+    </row>
+    <row r="275">
+      <c r="C275" s="6" t="n"/>
+      <c r="D275" s="6" t="n"/>
+    </row>
+    <row r="276">
+      <c r="C276" s="6" t="n"/>
+      <c r="D276" s="6" t="n"/>
+    </row>
+    <row r="277">
+      <c r="C277" s="6" t="n"/>
+      <c r="D277" s="6" t="n"/>
+    </row>
+    <row r="278">
+      <c r="C278" s="6" t="n"/>
+      <c r="D278" s="6" t="n"/>
+    </row>
+    <row r="279">
+      <c r="C279" s="6" t="n"/>
+      <c r="D279" s="6" t="n"/>
+    </row>
+    <row r="280">
+      <c r="C280" s="6" t="n"/>
+      <c r="D280" s="6" t="n"/>
+    </row>
+    <row r="281">
+      <c r="C281" s="6" t="n"/>
+      <c r="D281" s="6" t="n"/>
+    </row>
+    <row r="282">
+      <c r="C282" s="6" t="n"/>
+      <c r="D282" s="6" t="n"/>
+    </row>
+    <row r="283">
+      <c r="C283" s="6" t="n"/>
+      <c r="D283" s="6" t="n"/>
+    </row>
+    <row r="284">
+      <c r="C284" s="6" t="n"/>
+      <c r="D284" s="6" t="n"/>
+    </row>
+    <row r="285">
+      <c r="C285" s="6" t="n"/>
+      <c r="D285" s="6" t="n"/>
+    </row>
+    <row r="286">
+      <c r="C286" s="6" t="n"/>
+      <c r="D286" s="6" t="n"/>
+    </row>
+    <row r="287">
+      <c r="C287" s="6" t="n"/>
+      <c r="D287" s="6" t="n"/>
+    </row>
+    <row r="288">
+      <c r="C288" s="6" t="n"/>
+      <c r="D288" s="6" t="n"/>
+    </row>
+    <row r="289">
+      <c r="C289" s="6" t="n"/>
+      <c r="D289" s="6" t="n"/>
+    </row>
+    <row r="290">
+      <c r="C290" s="6" t="n"/>
+      <c r="D290" s="6" t="n"/>
+    </row>
+    <row r="291">
+      <c r="C291" s="6" t="n"/>
+      <c r="D291" s="6" t="n"/>
+    </row>
+    <row r="292">
+      <c r="C292" s="6" t="n"/>
+      <c r="D292" s="6" t="n"/>
+    </row>
+    <row r="293">
+      <c r="C293" s="6" t="n"/>
+      <c r="D293" s="6" t="n"/>
+    </row>
+    <row r="294">
+      <c r="C294" s="6" t="n"/>
+      <c r="D294" s="6" t="n"/>
+    </row>
+    <row r="295">
+      <c r="C295" s="6" t="n"/>
+      <c r="D295" s="6" t="n"/>
+    </row>
+    <row r="296">
+      <c r="C296" s="6" t="n"/>
+      <c r="D296" s="6" t="n"/>
+    </row>
+    <row r="297">
+      <c r="C297" s="6" t="n"/>
+      <c r="D297" s="6" t="n"/>
+    </row>
+    <row r="298">
+      <c r="C298" s="6" t="n"/>
+      <c r="D298" s="6" t="n"/>
+    </row>
+    <row r="299">
+      <c r="C299" s="6" t="n"/>
+      <c r="D299" s="6" t="n"/>
+    </row>
+    <row r="300">
+      <c r="C300" s="6" t="n"/>
+      <c r="D300" s="6" t="n"/>
+    </row>
+    <row r="301">
+      <c r="C301" s="6" t="n"/>
+      <c r="D301" s="6" t="n"/>
+    </row>
+    <row r="302">
+      <c r="C302" s="6" t="n"/>
+      <c r="D302" s="6" t="n"/>
+    </row>
+    <row r="303">
+      <c r="C303" s="6" t="n"/>
+      <c r="D303" s="6" t="n"/>
+    </row>
+    <row r="304">
+      <c r="C304" s="6" t="n"/>
+      <c r="D304" s="6" t="n"/>
+    </row>
+    <row r="305">
+      <c r="C305" s="6" t="n"/>
+      <c r="D305" s="6" t="n"/>
+    </row>
+    <row r="306">
+      <c r="C306" s="6" t="n"/>
+      <c r="D306" s="6" t="n"/>
+    </row>
+    <row r="307">
+      <c r="C307" s="6" t="n"/>
+      <c r="D307" s="6" t="n"/>
+    </row>
+    <row r="308">
+      <c r="C308" s="6" t="n"/>
+      <c r="D308" s="6" t="n"/>
+    </row>
+    <row r="309">
+      <c r="C309" s="6" t="n"/>
+      <c r="D309" s="6" t="n"/>
+    </row>
+    <row r="310">
+      <c r="C310" s="6" t="n"/>
+      <c r="D310" s="6" t="n"/>
+    </row>
+    <row r="311">
+      <c r="C311" s="6" t="n"/>
+      <c r="D311" s="6" t="n"/>
+    </row>
+    <row r="312">
+      <c r="C312" s="6" t="n"/>
+      <c r="D312" s="6" t="n"/>
+    </row>
+    <row r="313">
+      <c r="C313" s="6" t="n"/>
+      <c r="D313" s="6" t="n"/>
+    </row>
+    <row r="314">
+      <c r="C314" s="6" t="n"/>
+      <c r="D314" s="6" t="n"/>
+    </row>
+    <row r="315">
+      <c r="C315" s="6" t="n"/>
+      <c r="D315" s="6" t="n"/>
+    </row>
+    <row r="316">
+      <c r="C316" s="6" t="n"/>
+      <c r="D316" s="6" t="n"/>
+    </row>
+    <row r="317">
+      <c r="C317" s="6" t="n"/>
+      <c r="D317" s="6" t="n"/>
+    </row>
+    <row r="318">
+      <c r="C318" s="6" t="n"/>
+      <c r="D318" s="6" t="n"/>
+    </row>
+    <row r="319">
+      <c r="C319" s="6" t="n"/>
+      <c r="D319" s="6" t="n"/>
+    </row>
+    <row r="320">
+      <c r="C320" s="6" t="n"/>
+      <c r="D320" s="6" t="n"/>
+    </row>
+    <row r="321">
+      <c r="C321" s="6" t="n"/>
+      <c r="D321" s="6" t="n"/>
+    </row>
+    <row r="322">
+      <c r="C322" s="6" t="n"/>
+      <c r="D322" s="6" t="n"/>
+    </row>
+    <row r="323">
+      <c r="C323" s="6" t="n"/>
+      <c r="D323" s="6" t="n"/>
+    </row>
+    <row r="324">
+      <c r="C324" s="6" t="n"/>
+      <c r="D324" s="6" t="n"/>
+    </row>
+    <row r="325">
+      <c r="C325" s="6" t="n"/>
+      <c r="D325" s="6" t="n"/>
+    </row>
+    <row r="326">
+      <c r="C326" s="6" t="n"/>
+      <c r="D326" s="6" t="n"/>
+    </row>
+    <row r="327">
+      <c r="C327" s="6" t="n"/>
+      <c r="D327" s="6" t="n"/>
+    </row>
+    <row r="328">
+      <c r="C328" s="6" t="n"/>
+      <c r="D328" s="6" t="n"/>
+    </row>
+    <row r="329">
+      <c r="C329" s="6" t="n"/>
+      <c r="D329" s="6" t="n"/>
+    </row>
+    <row r="330">
+      <c r="C330" s="6" t="n"/>
+      <c r="D330" s="6" t="n"/>
+    </row>
+    <row r="331">
+      <c r="C331" s="6" t="n"/>
+      <c r="D331" s="6" t="n"/>
+    </row>
+    <row r="332">
+      <c r="C332" s="6" t="n"/>
+      <c r="D332" s="6" t="n"/>
+    </row>
+    <row r="333">
+      <c r="C333" s="6" t="n"/>
+      <c r="D333" s="6" t="n"/>
+    </row>
+    <row r="334">
+      <c r="C334" s="6" t="n"/>
+      <c r="D334" s="6" t="n"/>
+    </row>
+    <row r="335">
+      <c r="C335" s="6" t="n"/>
+      <c r="D335" s="6" t="n"/>
+    </row>
+    <row r="336">
+      <c r="C336" s="6" t="n"/>
+      <c r="D336" s="6" t="n"/>
+    </row>
+    <row r="337">
+      <c r="C337" s="6" t="n"/>
+      <c r="D337" s="6" t="n"/>
+    </row>
+    <row r="338">
+      <c r="C338" s="6" t="n"/>
+      <c r="D338" s="6" t="n"/>
+    </row>
+    <row r="339">
+      <c r="C339" s="6" t="n"/>
+      <c r="D339" s="6" t="n"/>
+    </row>
+    <row r="340">
+      <c r="C340" s="6" t="n"/>
+      <c r="D340" s="6" t="n"/>
+    </row>
+    <row r="341">
+      <c r="C341" s="6" t="n"/>
+      <c r="D341" s="6" t="n"/>
+    </row>
+    <row r="342">
+      <c r="C342" s="6" t="n"/>
+      <c r="D342" s="6" t="n"/>
+    </row>
+    <row r="343">
+      <c r="C343" s="6" t="n"/>
+      <c r="D343" s="6" t="n"/>
+    </row>
+    <row r="344">
+      <c r="C344" s="6" t="n"/>
+      <c r="D344" s="6" t="n"/>
+    </row>
+    <row r="345">
+      <c r="C345" s="6" t="n"/>
+      <c r="D345" s="6" t="n"/>
+    </row>
+    <row r="346">
+      <c r="C346" s="6" t="n"/>
+      <c r="D346" s="6" t="n"/>
+    </row>
+    <row r="347">
+      <c r="C347" s="6" t="n"/>
+      <c r="D347" s="6" t="n"/>
+    </row>
+    <row r="348">
+      <c r="C348" s="6" t="n"/>
+      <c r="D348" s="6" t="n"/>
+    </row>
+    <row r="349">
+      <c r="C349" s="6" t="n"/>
+      <c r="D349" s="6" t="n"/>
+    </row>
+    <row r="350">
+      <c r="C350" s="6" t="n"/>
+      <c r="D350" s="6" t="n"/>
+    </row>
+    <row r="351">
+      <c r="C351" s="6" t="n"/>
+      <c r="D351" s="6" t="n"/>
+    </row>
+    <row r="352">
+      <c r="C352" s="6" t="n"/>
+      <c r="D352" s="6" t="n"/>
+    </row>
+    <row r="353">
+      <c r="C353" s="6" t="n"/>
+      <c r="D353" s="6" t="n"/>
+    </row>
+    <row r="354">
+      <c r="C354" s="6" t="n"/>
+      <c r="D354" s="6" t="n"/>
+    </row>
+    <row r="355">
+      <c r="C355" s="6" t="n"/>
+      <c r="D355" s="6" t="n"/>
+    </row>
+    <row r="356">
+      <c r="C356" s="6" t="n"/>
+      <c r="D356" s="6" t="n"/>
+    </row>
+    <row r="357">
+      <c r="C357" s="6" t="n"/>
+      <c r="D357" s="6" t="n"/>
+    </row>
+    <row r="358">
+      <c r="C358" s="6" t="n"/>
+      <c r="D358" s="6" t="n"/>
+    </row>
+    <row r="359">
+      <c r="C359" s="6" t="n"/>
+      <c r="D359" s="6" t="n"/>
+    </row>
+    <row r="360">
+      <c r="C360" s="6" t="n"/>
+      <c r="D360" s="6" t="n"/>
+    </row>
+    <row r="361">
+      <c r="C361" s="6" t="n"/>
+      <c r="D361" s="6" t="n"/>
+    </row>
+    <row r="362">
+      <c r="C362" s="6" t="n"/>
+      <c r="D362" s="6" t="n"/>
+    </row>
+    <row r="363">
+      <c r="C363" s="6" t="n"/>
+      <c r="D363" s="6" t="n"/>
+    </row>
+    <row r="364">
+      <c r="C364" s="6" t="n"/>
+      <c r="D364" s="6" t="n"/>
+    </row>
+    <row r="365">
+      <c r="C365" s="6" t="n"/>
+      <c r="D365" s="6" t="n"/>
+    </row>
+    <row r="366">
+      <c r="C366" s="6" t="n"/>
+      <c r="D366" s="6" t="n"/>
+    </row>
+    <row r="367">
+      <c r="C367" s="6" t="n"/>
+      <c r="D367" s="6" t="n"/>
+    </row>
+    <row r="368">
+      <c r="C368" s="6" t="n"/>
+      <c r="D368" s="6" t="n"/>
+    </row>
+    <row r="369">
+      <c r="C369" s="6" t="n"/>
+      <c r="D369" s="6" t="n"/>
+    </row>
+    <row r="370">
+      <c r="C370" s="6" t="n"/>
+      <c r="D370" s="6" t="n"/>
+    </row>
+    <row r="371">
+      <c r="C371" s="6" t="n"/>
+      <c r="D371" s="6" t="n"/>
+    </row>
+    <row r="372">
+      <c r="C372" s="6" t="n"/>
+      <c r="D372" s="6" t="n"/>
+    </row>
+    <row r="373">
+      <c r="C373" s="6" t="n"/>
+      <c r="D373" s="6" t="n"/>
+    </row>
+    <row r="374">
+      <c r="C374" s="6" t="n"/>
+      <c r="D374" s="6" t="n"/>
+    </row>
+    <row r="375">
+      <c r="C375" s="6" t="n"/>
+      <c r="D375" s="6" t="n"/>
+    </row>
+    <row r="376">
+      <c r="C376" s="6" t="n"/>
+      <c r="D376" s="6" t="n"/>
+    </row>
+    <row r="377">
+      <c r="C377" s="6" t="n"/>
+      <c r="D377" s="6" t="n"/>
+    </row>
+    <row r="378">
+      <c r="C378" s="6" t="n"/>
+      <c r="D378" s="6" t="n"/>
+    </row>
+    <row r="379">
+      <c r="C379" s="6" t="n"/>
+      <c r="D379" s="6" t="n"/>
+    </row>
+    <row r="380">
+      <c r="C380" s="6" t="n"/>
+      <c r="D380" s="6" t="n"/>
+    </row>
+    <row r="381">
+      <c r="C381" s="6" t="n"/>
+      <c r="D381" s="6" t="n"/>
+    </row>
+    <row r="382">
+      <c r="C382" s="6" t="n"/>
+      <c r="D382" s="6" t="n"/>
+    </row>
+    <row r="383">
+      <c r="C383" s="6" t="n"/>
+      <c r="D383" s="6" t="n"/>
+    </row>
+    <row r="384">
+      <c r="C384" s="6" t="n"/>
+      <c r="D384" s="6" t="n"/>
+    </row>
+    <row r="385">
+      <c r="C385" s="6" t="n"/>
+      <c r="D385" s="6" t="n"/>
+    </row>
+    <row r="386">
+      <c r="C386" s="6" t="n"/>
+      <c r="D386" s="6" t="n"/>
+    </row>
+    <row r="387">
+      <c r="C387" s="6" t="n"/>
+      <c r="D387" s="6" t="n"/>
+    </row>
+    <row r="388">
+      <c r="C388" s="6" t="n"/>
+      <c r="D388" s="6" t="n"/>
+    </row>
+    <row r="389">
+      <c r="C389" s="6" t="n"/>
+      <c r="D389" s="6" t="n"/>
+    </row>
+    <row r="390">
+      <c r="C390" s="6" t="n"/>
+      <c r="D390" s="6" t="n"/>
+    </row>
+    <row r="391">
+      <c r="C391" s="6" t="n"/>
+      <c r="D391" s="6" t="n"/>
+    </row>
+    <row r="392">
+      <c r="C392" s="6" t="n"/>
+      <c r="D392" s="6" t="n"/>
+    </row>
+    <row r="393">
+      <c r="C393" s="6" t="n"/>
+      <c r="D393" s="6" t="n"/>
+    </row>
+    <row r="394">
+      <c r="C394" s="6" t="n"/>
+      <c r="D394" s="6" t="n"/>
+    </row>
+    <row r="395">
+      <c r="C395" s="6" t="n"/>
+      <c r="D395" s="6" t="n"/>
+    </row>
+    <row r="396">
+      <c r="C396" s="6" t="n"/>
+      <c r="D396" s="6" t="n"/>
+    </row>
+    <row r="397">
+      <c r="C397" s="6" t="n"/>
+      <c r="D397" s="6" t="n"/>
+    </row>
+    <row r="398">
+      <c r="C398" s="6" t="n"/>
+      <c r="D398" s="6" t="n"/>
+    </row>
+    <row r="399">
+      <c r="C399" s="6" t="n"/>
+      <c r="D399" s="6" t="n"/>
+    </row>
+    <row r="400">
+      <c r="C400" s="6" t="n"/>
+      <c r="D400" s="6" t="n"/>
+    </row>
+    <row r="401">
+      <c r="C401" s="6" t="n"/>
+      <c r="D401" s="6" t="n"/>
+    </row>
+    <row r="402">
+      <c r="C402" s="6" t="n"/>
+      <c r="D402" s="6" t="n"/>
+    </row>
+    <row r="403">
+      <c r="C403" s="6" t="n"/>
+      <c r="D403" s="6" t="n"/>
+    </row>
+    <row r="404">
+      <c r="C404" s="6" t="n"/>
+      <c r="D404" s="6" t="n"/>
+    </row>
+    <row r="405">
+      <c r="C405" s="6" t="n"/>
+      <c r="D405" s="6" t="n"/>
+    </row>
+    <row r="406">
+      <c r="C406" s="6" t="n"/>
+      <c r="D406" s="6" t="n"/>
+    </row>
+    <row r="407">
+      <c r="C407" s="6" t="n"/>
+      <c r="D407" s="6" t="n"/>
+    </row>
+    <row r="408">
+      <c r="C408" s="6" t="n"/>
+      <c r="D408" s="6" t="n"/>
+    </row>
+    <row r="409">
+      <c r="C409" s="6" t="n"/>
+      <c r="D409" s="6" t="n"/>
+    </row>
+    <row r="410">
+      <c r="C410" s="6" t="n"/>
+      <c r="D410" s="6" t="n"/>
+    </row>
+    <row r="411">
+      <c r="C411" s="6" t="n"/>
+      <c r="D411" s="6" t="n"/>
+    </row>
+    <row r="412">
+      <c r="C412" s="6" t="n"/>
+      <c r="D412" s="6" t="n"/>
+    </row>
+    <row r="413">
+      <c r="C413" s="6" t="n"/>
+      <c r="D413" s="6" t="n"/>
+    </row>
+    <row r="414">
+      <c r="C414" s="6" t="n"/>
+      <c r="D414" s="6" t="n"/>
+    </row>
+    <row r="415">
+      <c r="C415" s="6" t="n"/>
+      <c r="D415" s="6" t="n"/>
+    </row>
+    <row r="416">
+      <c r="C416" s="6" t="n"/>
+      <c r="D416" s="6" t="n"/>
+    </row>
+    <row r="417">
+      <c r="C417" s="6" t="n"/>
+      <c r="D417" s="6" t="n"/>
+    </row>
+    <row r="418">
+      <c r="C418" s="6" t="n"/>
+      <c r="D418" s="6" t="n"/>
+    </row>
+    <row r="419">
+      <c r="C419" s="6" t="n"/>
+      <c r="D419" s="6" t="n"/>
+    </row>
+    <row r="420">
+      <c r="C420" s="6" t="n"/>
+      <c r="D420" s="6" t="n"/>
+    </row>
+    <row r="421">
+      <c r="C421" s="6" t="n"/>
+      <c r="D421" s="6" t="n"/>
+    </row>
+    <row r="422">
+      <c r="C422" s="6" t="n"/>
+      <c r="D422" s="6" t="n"/>
+    </row>
+    <row r="423">
+      <c r="C423" s="6" t="n"/>
+      <c r="D423" s="6" t="n"/>
+    </row>
+    <row r="424">
+      <c r="C424" s="6" t="n"/>
+      <c r="D424" s="6" t="n"/>
+    </row>
+    <row r="425">
+      <c r="C425" s="6" t="n"/>
+      <c r="D425" s="6" t="n"/>
+    </row>
+    <row r="426">
+      <c r="C426" s="6" t="n"/>
+      <c r="D426" s="6" t="n"/>
+    </row>
+    <row r="427">
+      <c r="C427" s="6" t="n"/>
+      <c r="D427" s="6" t="n"/>
+    </row>
+    <row r="428">
+      <c r="C428" s="6" t="n"/>
+      <c r="D428" s="6" t="n"/>
+    </row>
+    <row r="429">
+      <c r="C429" s="6" t="n"/>
+      <c r="D429" s="6" t="n"/>
+    </row>
+    <row r="430">
+      <c r="C430" s="6" t="n"/>
+      <c r="D430" s="6" t="n"/>
+    </row>
+    <row r="431">
+      <c r="C431" s="6" t="n"/>
+      <c r="D431" s="6" t="n"/>
+    </row>
+    <row r="432">
+      <c r="C432" s="6" t="n"/>
+      <c r="D432" s="6" t="n"/>
+    </row>
+    <row r="433">
+      <c r="C433" s="6" t="n"/>
+      <c r="D433" s="6" t="n"/>
+    </row>
+    <row r="434">
+      <c r="C434" s="6" t="n"/>
+      <c r="D434" s="6" t="n"/>
+    </row>
+    <row r="435">
+      <c r="C435" s="6" t="n"/>
+      <c r="D435" s="6" t="n"/>
+    </row>
+    <row r="436">
+      <c r="C436" s="6" t="n"/>
+      <c r="D436" s="6" t="n"/>
+    </row>
+    <row r="437">
+      <c r="C437" s="6" t="n"/>
+      <c r="D437" s="6" t="n"/>
+    </row>
+    <row r="438">
+      <c r="C438" s="6" t="n"/>
+      <c r="D438" s="6" t="n"/>
+    </row>
+    <row r="439">
+      <c r="C439" s="6" t="n"/>
+      <c r="D439" s="6" t="n"/>
+    </row>
+    <row r="440">
+      <c r="C440" s="6" t="n"/>
+      <c r="D440" s="6" t="n"/>
+    </row>
+    <row r="441">
+      <c r="C441" s="6" t="n"/>
+      <c r="D441" s="6" t="n"/>
+    </row>
+    <row r="442">
+      <c r="C442" s="6" t="n"/>
+      <c r="D442" s="6" t="n"/>
+    </row>
+    <row r="443">
+      <c r="C443" s="6" t="n"/>
+      <c r="D443" s="6" t="n"/>
+    </row>
+    <row r="444">
+      <c r="C444" s="6" t="n"/>
+      <c r="D444" s="6" t="n"/>
+    </row>
+    <row r="445">
+      <c r="C445" s="6" t="n"/>
+      <c r="D445" s="6" t="n"/>
+    </row>
+    <row r="446">
+      <c r="C446" s="6" t="n"/>
+      <c r="D446" s="6" t="n"/>
+    </row>
+    <row r="447">
+      <c r="C447" s="6" t="n"/>
+      <c r="D447" s="6" t="n"/>
+    </row>
+    <row r="448">
+      <c r="C448" s="6" t="n"/>
+      <c r="D448" s="6" t="n"/>
+    </row>
+    <row r="449">
+      <c r="C449" s="6" t="n"/>
+      <c r="D449" s="6" t="n"/>
+    </row>
+    <row r="450">
+      <c r="C450" s="6" t="n"/>
+      <c r="D450" s="6" t="n"/>
+    </row>
+    <row r="451">
+      <c r="C451" s="6" t="n"/>
+      <c r="D451" s="6" t="n"/>
+    </row>
+    <row r="452">
+      <c r="C452" s="6" t="n"/>
+      <c r="D452" s="6" t="n"/>
+    </row>
+    <row r="453">
+      <c r="C453" s="6" t="n"/>
+      <c r="D453" s="6" t="n"/>
+    </row>
+    <row r="454">
+      <c r="C454" s="6" t="n"/>
+      <c r="D454" s="6" t="n"/>
+    </row>
+    <row r="455">
+      <c r="C455" s="6" t="n"/>
+      <c r="D455" s="6" t="n"/>
+    </row>
+    <row r="456">
+      <c r="C456" s="6" t="n"/>
+      <c r="D456" s="6" t="n"/>
+    </row>
+    <row r="457">
+      <c r="C457" s="6" t="n"/>
+      <c r="D457" s="6" t="n"/>
+    </row>
+    <row r="458">
+      <c r="C458" s="6" t="n"/>
+      <c r="D458" s="6" t="n"/>
+    </row>
+    <row r="459">
+      <c r="C459" s="6" t="n"/>
+      <c r="D459" s="6" t="n"/>
+    </row>
+    <row r="460">
+      <c r="C460" s="6" t="n"/>
+      <c r="D460" s="6" t="n"/>
+    </row>
+    <row r="461">
+      <c r="C461" s="6" t="n"/>
+      <c r="D461" s="6" t="n"/>
+    </row>
+    <row r="462">
+      <c r="C462" s="6" t="n"/>
+      <c r="D462" s="6" t="n"/>
+    </row>
+    <row r="463">
+      <c r="C463" s="6" t="n"/>
+      <c r="D463" s="6" t="n"/>
+    </row>
+    <row r="464">
+      <c r="C464" s="6" t="n"/>
+      <c r="D464" s="6" t="n"/>
+    </row>
+    <row r="465">
+      <c r="C465" s="6" t="n"/>
+      <c r="D465" s="6" t="n"/>
+    </row>
+    <row r="466">
+      <c r="C466" s="6" t="n"/>
+      <c r="D466" s="6" t="n"/>
+    </row>
+    <row r="467">
+      <c r="C467" s="6" t="n"/>
+      <c r="D467" s="6" t="n"/>
+    </row>
+    <row r="468">
+      <c r="C468" s="6" t="n"/>
+      <c r="D468" s="6" t="n"/>
+    </row>
+    <row r="469">
+      <c r="C469" s="6" t="n"/>
+      <c r="D469" s="6" t="n"/>
+    </row>
+    <row r="470">
+      <c r="C470" s="6" t="n"/>
+      <c r="D470" s="6" t="n"/>
+    </row>
+    <row r="471">
+      <c r="C471" s="6" t="n"/>
+      <c r="D471" s="6" t="n"/>
+    </row>
+    <row r="472">
+      <c r="C472" s="6" t="n"/>
+      <c r="D472" s="6" t="n"/>
+    </row>
+    <row r="473">
+      <c r="C473" s="6" t="n"/>
+      <c r="D473" s="6" t="n"/>
+    </row>
+    <row r="474">
+      <c r="C474" s="6" t="n"/>
+      <c r="D474" s="6" t="n"/>
+    </row>
+    <row r="475">
+      <c r="C475" s="6" t="n"/>
+      <c r="D475" s="6" t="n"/>
+    </row>
+    <row r="476">
+      <c r="C476" s="6" t="n"/>
+      <c r="D476" s="6" t="n"/>
+    </row>
+    <row r="477">
+      <c r="C477" s="6" t="n"/>
+      <c r="D477" s="6" t="n"/>
+    </row>
+    <row r="478">
+      <c r="C478" s="6" t="n"/>
+      <c r="D478" s="6" t="n"/>
+    </row>
+    <row r="479">
+      <c r="C479" s="6" t="n"/>
+      <c r="D479" s="6" t="n"/>
+    </row>
+    <row r="480">
+      <c r="C480" s="6" t="n"/>
+      <c r="D480" s="6" t="n"/>
+    </row>
+    <row r="481">
+      <c r="C481" s="6" t="n"/>
+      <c r="D481" s="6" t="n"/>
+    </row>
+    <row r="482">
+      <c r="C482" s="6" t="n"/>
+      <c r="D482" s="6" t="n"/>
+    </row>
+    <row r="483">
+      <c r="C483" s="6" t="n"/>
+      <c r="D483" s="6" t="n"/>
+    </row>
+    <row r="484">
+      <c r="C484" s="6" t="n"/>
+      <c r="D484" s="6" t="n"/>
+    </row>
+    <row r="485">
+      <c r="C485" s="6" t="n"/>
+      <c r="D485" s="6" t="n"/>
+    </row>
+    <row r="486">
+      <c r="C486" s="6" t="n"/>
+      <c r="D486" s="6" t="n"/>
+    </row>
+    <row r="487">
+      <c r="C487" s="6" t="n"/>
+      <c r="D487" s="6" t="n"/>
+    </row>
+    <row r="488">
+      <c r="C488" s="6" t="n"/>
+      <c r="D488" s="6" t="n"/>
+    </row>
+    <row r="489">
+      <c r="C489" s="6" t="n"/>
+      <c r="D489" s="6" t="n"/>
+    </row>
+    <row r="490">
+      <c r="C490" s="6" t="n"/>
+      <c r="D490" s="6" t="n"/>
+    </row>
+    <row r="491">
+      <c r="C491" s="6" t="n"/>
+      <c r="D491" s="6" t="n"/>
+    </row>
+    <row r="492">
+      <c r="C492" s="6" t="n"/>
+      <c r="D492" s="6" t="n"/>
+    </row>
+    <row r="493">
+      <c r="C493" s="6" t="n"/>
+      <c r="D493" s="6" t="n"/>
+    </row>
+    <row r="494">
+      <c r="C494" s="6" t="n"/>
+      <c r="D494" s="6" t="n"/>
+    </row>
+    <row r="495">
+      <c r="C495" s="6" t="n"/>
+      <c r="D495" s="6" t="n"/>
+    </row>
+    <row r="496">
+      <c r="C496" s="6" t="n"/>
+      <c r="D496" s="6" t="n"/>
+    </row>
+    <row r="497">
+      <c r="C497" s="6" t="n"/>
+      <c r="D497" s="6" t="n"/>
+    </row>
+    <row r="498">
+      <c r="C498" s="6" t="n"/>
+      <c r="D498" s="6" t="n"/>
+    </row>
+    <row r="499">
+      <c r="C499" s="6" t="n"/>
+      <c r="D499" s="6" t="n"/>
+    </row>
+    <row r="500">
+      <c r="C500" s="6" t="n"/>
+      <c r="D500" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -560,7 +2565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -573,6 +2578,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -580,10 +2586,11 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Εργαλείο: Ενέργειες MySchool → Ε7. Καταχώρηση Απουσίας σε Οργανική.</t>
+          <t>Εργαλείο: Ενέργειες MySchool → Ε6. Καταχώρηση Απουσίας σε Οργανική.</t>
         </is>
       </c>
     </row>
@@ -600,26 +2607,33 @@
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Υποχρεωτικές στήλες: Α.Μ., Σχέση τοποθέτησης, Έως.</t>
+          <t>Υποχρεωτικές στήλες: Α.Μ., Σχέση τοποθέτησης, Από, Έως.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>«Από» και «Έως» = οι ημερομηνίες που θα μπουν στα πεδία «Ισχύει από» / «Ισχύει έως» της απουσίας (μορφή Η/Μ/ΕΕΕΕ, π.χ. 1/9/2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>Το αρχείο μπορεί να έχει πάνω από μία γραμμή ανά εκπαιδευτικό (π.χ. Οργανική + Ολική Διάθεση) — το εργαλείο εντοπίζει μόνος του τη σωστή γραμμή ανά Α.Μ.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>ΔΕΝ χρειάζεται να περιλαμβάνεται γραμμή «Οργανικά» — αυτή αναζητείται απευθείας στο MySchool.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>Δεκτά αρχεία: .xlsx, .xls, .csv.</t>
         </is>
